--- a/tkb_truong.xlsx
+++ b/tkb_truong.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\2025 -  2026\ke thay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E08585-090F-47CE-9F83-0E49A514C75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AE86B2-E415-4A40-AB50-D2334BC46AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="15375" windowHeight="7785" xr2:uid="{D4501D93-A4DF-42E9-8A9F-AD9C6094AE09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D4501D93-A4DF-42E9-8A9F-AD9C6094AE09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>Tiết</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Đỗ Đặng Toàn</t>
   </si>
   <si>
-    <t>9A4 - Tin học</t>
-  </si>
-  <si>
     <t>6A4 - Tin học</t>
   </si>
   <si>
@@ -105,12 +102,6 @@
     <t>6A3 - Tin học</t>
   </si>
   <si>
-    <t>9A2 - Tin học</t>
-  </si>
-  <si>
-    <t>9A2 - GDĐP</t>
-  </si>
-  <si>
     <t>8A4 - Tin học</t>
   </si>
   <si>
@@ -120,9 +111,6 @@
     <t>8A2 - Tin học</t>
   </si>
   <si>
-    <t>9A1 - Tin học</t>
-  </si>
-  <si>
     <t>7A1 - Tin học</t>
   </si>
   <si>
@@ -133,9 +121,6 @@
   </si>
   <si>
     <t>7A4 - Tin học</t>
-  </si>
-  <si>
-    <t>9A3 - Tin học</t>
   </si>
   <si>
     <t>8A1 - Tin học</t>
@@ -1126,9 +1111,11 @@
       </c>
       <c r="C3" s="1"/>
       <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7">
@@ -1140,9 +1127,6 @@
       </c>
       <c r="C4" s="1"/>
       <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="1"/>
@@ -1159,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -1197,13 +1181,14 @@
         <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1216,13 +1201,18 @@
       <c r="C9" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
@@ -1232,15 +1222,20 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
@@ -1250,15 +1245,17 @@
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
